--- a/Tablas/Tablas_Stock_2026_06.xlsx
+++ b/Tablas/Tablas_Stock_2026_06.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Satisfaccion global 70% (+6pp vs mayo). Muestra en maduracion: tasa de respuesta 3.5% (149 respuestas), las 7 areas por debajo del 5%. Dato publicado con reserva por representatividad.</t>
+          <t>Satisfaccion global 70% (+6pp vs mayo). (*) Muestra escasa: en junio se registraron inconvenientes tecnicos en la toma de encuestas, sumado a la maduracion natural de respuestas. Tasa 3.5% (149 resp.), 7 areas &lt;5%. Dato con reserva.</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Tasa de respuesta de encuesta 3.5% en Jun-2026 (149 respuestas sobre 4309 incidentes); las 7 areas del monitor quedan por debajo del 5%. La baja responde a la maduracion de la encuesta (las respuestas de Jun-2026 aun no se acumularon al corte), no a una caida de satisfaccion. La satisfaccion por area se publica con la marca '(muestra insuficiente)'.</t>
+          <t>Tasa de respuesta de encuesta 3.5% en Jun-2026 (149 respuestas sobre 4309 incidentes); las 7 areas del monitor quedan por debajo del 5%. Dos causas: inconvenientes tecnicos en la toma de encuestas durante Jun-2026 y la maduracion natural de las respuestas (las cargadas en Jun-2026 aun no se acumularon al corte). No refleja caida de satisfaccion. La satisfaccion por area se publica con la marca '(muestra insuficiente)'.</t>
         </is>
       </c>
     </row>

--- a/Tablas/Tablas_Stock_2026_06.xlsx
+++ b/Tablas/Tablas_Stock_2026_06.xlsx
@@ -31,7 +31,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,18 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -61,11 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +496,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SLA global 38% (-6pp vs mayo). ARBOLADO 76% y CTRL ESPACIO 61% lideran; ALUMBRADO 55%. Mas bajos: RESIDUOS 31% y TRANSITO 38%. Promedio 4 dias para cerrados.</t>
+          <t>SLA global 38% (-6pp vs mayo). ARBOLADO 76% y CTRL ESPACIO 61% lideran; ALUMBRADO 55%. Mas bajos: RESIDUOS 31% y TRANSITO 38%. Promedio 5 dias para cerrados.</t>
         </is>
       </c>
     </row>
@@ -494,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Satisfaccion global 70% (+6pp vs mayo). (*) Muestra escasa: en junio se registraron inconvenientes tecnicos en la toma de encuestas, sumado a la maduracion natural de respuestas. Tasa 3.5% (149 resp.), 7 areas &lt;5%. Dato con reserva.</t>
+          <t>Satisfaccion global 70% (+6pp vs mayo). La baja tasa de respuesta (3.5%, 7/7 areas bajo 5%) se debe a la caida de la app que envia la encuesta al cierre del reclamo, mas la maduracion de respuestas. No refleja caida real; dato con reserva.</t>
         </is>
       </c>
     </row>
@@ -536,7 +550,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cierre 89% sobre 493 incidentes; 'Luminaria superior e inferior apagada du' lidera con 303 casos (88% cierre). Gestion interna 56%.</t>
+          <t>Cierre 89% sobre 493 incidentes; 'Luminaria sup. e inf. apagada de noche' lidera con 303 casos (88% cierre). Gestion interna 56%.</t>
         </is>
       </c>
     </row>
@@ -548,7 +562,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cierre bajo 40% sobre 124 incidentes; 'Árbol obstruye semáforo/luminaria/cartel' lidera con 46 casos (39% cierre). Sat 50% (muestra insuficiente).</t>
+          <t>Cierre bajo 40% sobre 124 incidentes; 'Arbol obstruye semaforo/luminaria/cartel' lidera con 46 casos (39% cierre). Sat 50% (muestra insuficiente).</t>
         </is>
       </c>
     </row>
@@ -560,7 +574,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cierre bajo 23% sobre 332 incidentes; 'Bache en calle de asfalto' lidera con 129 casos (24% cierre). Dias prom 9.0 elevado.</t>
+          <t>Cierre bajo 23% sobre 332 incidentes; 'Bache en calle de asfalto' lidera con 129 casos (24% cierre). Sat 62% (muestra insuficiente).</t>
         </is>
       </c>
     </row>
@@ -584,7 +598,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cierre 75% sobre 263 incidentes; 'Roedores en espacio público' lidera con 97 casos (95% cierre). Sat 40% (muestra insuficiente).</t>
+          <t>Cierre 75% sobre 263 incidentes; 'Roedores en espacio publico' lidera con 97 casos (95% cierre). Sat 40% (muestra insuficiente).</t>
         </is>
       </c>
     </row>
@@ -608,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cierre moderado 67% sobre 512 incidentes; 'Vehículos Abandonados' lidera con 405 casos (75% cierre). Sat 100% (muestra insuficiente).</t>
+          <t>Cierre moderado 67% sobre 512 incidentes; 'Vehiculos Abandonados' lidera con 405 casos (75% cierre). Sat 100% (muestra insuficiente).</t>
         </is>
       </c>
     </row>
@@ -623,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -667,418 +681,290 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>RESUELTA</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Feb-2026</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Arbolado y Plazas</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>% Cancelado &gt;10%</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>4% (sobre cerrados)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Cancelado baja a 4% de los cerrados en Jun-2026 (donut Cierres por Estado), dentro del rango operativo.</t>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Cancelado alto en cerrados</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>El cancelado baja a 4% de los cerrados en junio, dentro del rango operativo.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>RESUELTA</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Abr-2026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Calles y Veredas</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Cancelado alto en cerrados</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>El cancelado baja a 4% de los cerrados en junio, dentro del rango operativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>RESUELTA</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Abr-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Control del Espacio Publico</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Cancelado alto en cerrados</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>El cancelado baja a 1% de los cerrados en junio, dentro del rango operativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>RESUELTA</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Feb-2026</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Transito</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Cancelado excesivo</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>El cancelado baja a 9% de los cerrados en junio, dentro del rango operativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>RESUELTA</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>May-2026</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Transito</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cierre bajo en Vehiculo mal estacionado</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>El cierre del tipo sube de 0% a 67% entre mayo y junio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>PERSISTE</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Mar-2026</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Calles y Veredas</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Cierre colapsado</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>15% a 23%</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>El cierre del area sube de 15% a 23% entre mayo y junio; se mantiene en zona critica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Jun-2026</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Arbolado y Plazas</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Muestra encuesta insuficiente</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>consolidada</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Alerta de muestra por area consolidada en la alerta global de tasa de respuesta de encuesta (Jun-2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>RESUELTA</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Abr-2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Calles y Veredas</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Cancelado alto en cerrados</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4% (sobre cerrados)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Cancelado baja a 4% de los cerrados en Jun-2026 (donut Cierres por Estado), dentro del rango operativo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RESUELTA</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Abr-2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Calles y Veredas</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Muestra encuesta insuficiente</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>consolidada</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Alerta de muestra por area consolidada en la alerta global de tasa de respuesta de encuesta (Jun-2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RESUELTA</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Abr-2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Control del Espacio Publico</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Cancelado alto en cerrados</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1% (sobre cerrados)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Cancelado baja a 1% de los cerrados en Jun-2026 (donut Cierres por Estado), dentro del rango operativo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>RESUELTA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Feb-2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Transito</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>% Cancelado excesivo</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9% (sobre cerrados)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Cancelado baja a 9% de los cerrados en Jun-2026 (donut Cierres por Estado), dentro del rango operativo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>RESUELTA</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Abr-2026</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Transito</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Muestra encuesta insuficiente</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>consolidada</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Alerta de muestra por area consolidada en la alerta global de tasa de respuesta de encuesta (Jun-2026).</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Cierre bajo del area</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>El cierre del area se ubica en 40% en junio, el mas bajo despues de Calles y Veredas.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>RESUELTA</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>May-2026</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Transito</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Cierre bajo - Vehiculo mal estacionado</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Cierre del area sube de 0% a 67% (May-2026 a Jun-2026). Recuperacion significativa.</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Jun-2026</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Muestra de encuesta insuficiente (municipio)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Tasa 3.5%</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>La tasa de respuesta de encuesta de junio es 3.5%, con 149 respuestas sobre 4309 incidentes, y las 7 areas del monitor quedan por debajo del 5%. La causa principal es una caida de la aplicacion que envia la encuesta al cierre de cada reclamo, por lo que a muchos vecinos no se les envio la encuesta; a esto se suma la maduracion natural de las respuestas, que al corte aun no se habian acumulado. No refleja una caida real de la satisfaccion. Por eso la satisfaccion por area se publica con la marca (muestra insuficiente) y con reserva.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>PERSISTE</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Mar-2026</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Calles y Veredas</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Cierre colapsado</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>15%-&gt;23%</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Cierre del area 15%-&gt;23% (May-2026 a Jun-2026). Sigue en zona critica. Cancelado 4% sobre cerrados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Jun-2026</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Arbolado y Plazas</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Cierre bajo (area)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Cierre del area 40% en Jun-2026 (tablero). Cancelado 4% sobre cerrados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Jun-2026</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Calles y Veredas</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Dias promedio alto</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>9 dias</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Tiempo promedio de resolucion 9 dias en Jun-2026 (tablero). Por encima del tiempo habitual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Jun-2026</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Muestra de encuesta insuficiente (municipio)</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Tasa 3.5% (7/7 areas &lt;5%)</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Tasa de respuesta de encuesta 3.5% en Jun-2026 (149 respuestas sobre 4309 incidentes); las 7 areas del monitor quedan por debajo del 5%. Dos causas: inconvenientes tecnicos en la toma de encuestas durante Jun-2026 y la maduracion natural de las respuestas (las cargadas en Jun-2026 aun no se acumularon al corte). No refleja caida de satisfaccion. La satisfaccion por area se publica con la marca '(muestra insuficiente)'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Jun-2026</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Residuos y Limpieza</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Cierre bajo - Falta de recolección de residuos reciclables (Pr</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>22% (40 casos)</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Tipo 'Falta de recolección de residuos reciclables (Programa Día Verde)': 40 casos en Jun-2026 con 22% de cierre (tablero). Cierre muy por debajo del resto del area.</t>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Cierre bajo en Falta de recoleccion de residuos reciclables</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>El tipo del Programa Dia Verde tiene 40 casos con 22% de cierre en junio, muy por debajo del resto del area.</t>
         </is>
       </c>
     </row>
